--- a/web/public/forms/orig/o-mingan-dogeup.xlsx
+++ b/web/public/forms/orig/o-mingan-dogeup.xlsx
@@ -679,7 +679,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="39" t="inlineStr">

--- a/web/public/forms/orig/o-mingan-dogeup.xlsx
+++ b/web/public/forms/orig/o-mingan-dogeup.xlsx
@@ -9,12 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계약서" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일반조건" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-계약서" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'계약서'!$A$1:$L$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'일반조건'!$A$1:$L$256</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'예시-계약서'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -290,9 +288,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -757,10 +752,7 @@
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
-      <c r="J8" s="9">
-        <f>IF(OR(N(D7)=0,N(J7)=0),"",IF(J7&lt;D7,"⚠ 날짜 확인",J7-D7+1))</f>
-        <v/>
-      </c>
+      <c r="J8" s="9" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -773,10 +765,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="11">
-        <f>IF(N(D9)=0,"",D9)</f>
-        <v/>
-      </c>
+      <c r="G9" s="11" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -798,10 +787,7 @@
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="11">
-        <f>IF(N(D10)=0,"",D10)</f>
-        <v/>
-      </c>
+      <c r="G10" s="11" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -816,16 +802,10 @@
       </c>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="13">
-        <f>IF(N(D9)=0,"",D9-ROUND(D9/1.1,0))</f>
-        <v/>
-      </c>
+      <c r="D11" s="13" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="11">
-        <f>IF(N(D11)=0,"",D11)</f>
-        <v/>
-      </c>
+      <c r="G11" s="11" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -855,15 +835,9 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="15" t="n"/>
-      <c r="E14" s="13">
-        <f>IF(OR(N(D9)=0,N(D14)=0),"",ROUND(D9*D14/100,0))</f>
-        <v/>
-      </c>
+      <c r="E14" s="13" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="11">
-        <f>IF(N(E14)=0,"",E14)</f>
-        <v/>
-      </c>
+      <c r="G14" s="11" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
@@ -879,15 +853,9 @@
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="15" t="n"/>
-      <c r="E15" s="13">
-        <f>IF(OR(N(D9)=0,N(D15)=0),"",ROUND(D9*D15/100,0))</f>
-        <v/>
-      </c>
+      <c r="E15" s="13" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="11">
-        <f>IF(N(E15)=0,"",E15)</f>
-        <v/>
-      </c>
+      <c r="G15" s="11" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
@@ -960,10 +928,7 @@
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="22" t="n"/>
-      <c r="H19" s="23">
-        <f>IF(N(G19)&gt;10,"⚠ 100분의 10 이내의 범위에서 협의","* 100분의 10 이내의 범위에서 협의")</f>
-        <v/>
-      </c>
+      <c r="H19" s="23" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -1014,10 +979,7 @@
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="15" t="n"/>
-      <c r="H22" s="13">
-        <f>IF(OR(N(D22)=0,N(G22)=0),"",ROUND(D22*G22/100,0))</f>
-        <v/>
-      </c>
+      <c r="H22" s="13" t="n"/>
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="26" t="n"/>
@@ -1031,10 +993,7 @@
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="15" t="n"/>
-      <c r="H23" s="13">
-        <f>IF(OR(N(D23)=0,N(G23)=0),"",ROUND(D23*G23/100,0))</f>
-        <v/>
-      </c>
+      <c r="H23" s="13" t="n"/>
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="26" t="n"/>
@@ -1048,20 +1007,14 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="15" t="n"/>
-      <c r="H24" s="13">
-        <f>IF(OR(N(D24)=0,N(G24)=0),"",ROUND(D24*G24/100,0))</f>
-        <v/>
-      </c>
+      <c r="H24" s="13" t="n"/>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="26" t="n"/>
       <c r="L24" s="5" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="27">
-        <f>IF(OR(SUM(D22:D24)=0,N(D9)=0),"",IF(SUM(D22:D24)&lt;&gt;D9,"⚠ 공종별 계약금액의 합이 계약금액과 다릅니다.",""))</f>
-        <v/>
-      </c>
+      <c r="A25" s="27" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1106,10 +1059,7 @@
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="8">
-        <f>IF(D28="품목조정률","품목조정률 ■    지수조정률 □",IF(D28="지수조정률","품목조정률 □    지수조정률 ■","품목조정률 □    지수조정률 □"))</f>
-        <v/>
-      </c>
+      <c r="G28" s="8" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1237,6 +1187,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
@@ -3673,6 +3624,7 @@
         </is>
       </c>
     </row>
+    <row r="257"/>
     <row r="258" ht="34" customHeight="1">
       <c r="A258" s="14" t="inlineStr">
         <is>
@@ -3912,788 +3864,4 @@
     <brk id="231" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1"/>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>민간건설공사 표준도급계약서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>1. 공  사  명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>가나동 근린생활시설 신축공사</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2. 공 사 장 소</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>가나시 가나동 123-4 일원</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>3. 착공년월일</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="7" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>4. 준공예정년월일</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="7" t="n">
-        <v>46568</v>
-      </c>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="J8" s="9">
-        <f>IF(OR(N(D7)=0,N(J7)=0),"",IF(J7&lt;D7,"⚠ 날짜 확인",J7-D7+1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>5. 계약금액</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="10" t="n">
-        <v>2680000000</v>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="11">
-        <f>IF(N(D9)=0,"",D9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>(부가가치세 포함)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (노 무 비¹⁾)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="10" t="n">
-        <v>742500000</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="11">
-        <f>IF(N(D10)=0,"",D10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (부가가치세)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="13">
-        <f>IF(N(D9)=0,"",D9-ROUND(D9/1.1,0))</f>
-        <v/>
-      </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="11">
-        <f>IF(N(D11)=0,"",D11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ¹⁾ 건설산업기본법 제88조제2항, 동시행령 제84조제1항 규정에 의하여 산출한 노임</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ※ 부가가치세 = 계약금액 − 계약금액 ÷ 1.1 (원 단위 반올림)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>6. 계약보증금</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="13">
-        <f>IF(OR(N(D9)=0,N(D14)=0),"",ROUND(D9*D14/100,0))</f>
-        <v/>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="11">
-        <f>IF(N(E14)=0,"",E14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>7. 선      금</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E15" s="13">
-        <f>IF(OR(N(D9)=0,N(D15)=0),"",ROUND(D9*D15/100,0))</f>
-        <v/>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="11">
-        <f>IF(N(E15)=0,"",E15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>(계약체결 후</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>일 이내 지급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>8. 기성부분금</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>월에 1회</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>9. 지급자재의 품목 및 수량</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>10. 주요 원자재 가격변동에 따른 계약금액 연동을 위한 기준 비율</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="23">
-        <f>IF(N(G19)&gt;10,"⚠ 100분의 10 이내의 범위에서 협의","* 100분의 10 이내의 범위에서 협의")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>11. 하자담보책임 (복합공종인 경우 공종별로 구분 기재)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>공  종</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>공종별 계약금액</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>율(%)</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="inlineStr">
-        <is>
-          <t>하자보수보증금</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="25" t="inlineStr">
-        <is>
-          <t>하자담보책임기간</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>토목(배수로)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="10" t="n">
-        <v>2400000000</v>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="13">
-        <f>IF(OR(N(D22)=0,N(G22)=0),"",ROUND(D22*G22/100,0))</f>
-        <v/>
-      </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="26" t="inlineStr">
-        <is>
-          <t>5년</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>조경</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="10" t="n">
-        <v>280000000</v>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="13">
-        <f>IF(OR(N(D23)=0,N(G23)=0),"",ROUND(D23*G23/100,0))</f>
-        <v/>
-      </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="26" t="inlineStr">
-        <is>
-          <t>2년</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="26" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="13">
-        <f>IF(OR(N(D24)=0,N(G24)=0),"",ROUND(D24*G24/100,0))</f>
-        <v/>
-      </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="26" t="n"/>
-      <c r="L24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="27">
-        <f>IF(OR(SUM(D22:D24)=0,N(D9)=0),"",IF(SUM(D22:D24)&lt;&gt;D9,"⚠ 공종별 계약금액의 합이 계약금액과 다릅니다.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>12. 지체상금율</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>1,000분의 0.5 (1일)</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>* 따로 정하지 않으면 공공공사 계약의 지체상금율(일반조건 제30조④)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>13. 대가지급 지연 이자율</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>연 12%</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>14. 물가변동 적용기준</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>품목조정률</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="8">
-        <f>IF(D28="품목조정률","품목조정률 ■    지수조정률 □",IF(D28="지수조정률","품목조정률 □    지수조정률 ■","품목조정률 □    지수조정률 □"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>15. 기타사항</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>현장 여건에 따른 세부 사항은 공사계약특수조건에 따름</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="52.5" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>"도급인"과 "수급인"은 합의에 따라 붙임의 계약문서에 의하여 계약을 체결하고, 신의에 따라 성실히 계약상의 의무를 이행할 것을 확약하며, 이 계약의 증거로서 계약문서를 2통 작성하여 각 1통씩 보관한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>붙임서류 :</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>1. 민간건설공사 도급계약 일반조건 1부</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="inlineStr"/>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>2. 공사계약특수조건 1부</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="8" t="inlineStr"/>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>3. 설계서 및 산출내역서 1부</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="4" customHeight="1"/>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="31" t="n">
-        <v>46300</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>도  급  인</t>
-        </is>
-      </c>
-      <c r="G37" s="32" t="inlineStr">
-        <is>
-          <t>수  급  인</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>가나시 가나로 10</t>
-        </is>
-      </c>
-      <c r="G38" s="32" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H38" s="33" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="32" t="inlineStr">
-        <is>
-          <t>상호</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>예시개발(주)</t>
-        </is>
-      </c>
-      <c r="G39" s="32" t="inlineStr">
-        <is>
-          <t>상호</t>
-        </is>
-      </c>
-      <c r="H39" s="33" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>대표이사 홍길동</t>
-        </is>
-      </c>
-      <c r="F40" s="34" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="G40" s="32" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="H40" s="33" t="inlineStr">
-        <is>
-          <t>대표이사 김철수</t>
-        </is>
-      </c>
-      <c r="L40" s="34" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 사람).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="86">
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="H38:L38"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A12:L12"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="E17:L17"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="D5:L5"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:L27"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="H26:L26"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D18:L18"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D6:L6"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"품목조정률,지수조정률"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/orig/o-mingan-dogeup.xlsx
+++ b/web/public/forms/orig/o-mingan-dogeup.xlsx
@@ -674,7 +674,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
